--- a/Result/profitability/5521.xlsx
+++ b/Result/profitability/5521.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.11</v>
+        <v>0.14125</v>
       </c>
       <c r="N2" t="n">
-        <v>5.462499999999999</v>
+        <v>6.27</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06</v>
+        <v>0.115</v>
       </c>
       <c r="N3" t="n">
-        <v>4.864999999999999</v>
+        <v>5.79625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06125</v>
+        <v>0.12</v>
       </c>
       <c r="N4" t="n">
-        <v>4.05125</v>
+        <v>4.885</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.58</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.008749999999999994</v>
+        <v>0.02875</v>
       </c>
       <c r="N5" t="n">
-        <v>3.174999999999999</v>
+        <v>3.855</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.02499999999999999</v>
+        <v>0.0025</v>
       </c>
       <c r="N6" t="n">
-        <v>2.726249999999999</v>
+        <v>3.084999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04624999999999999</v>
+        <v>-0.008750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1025</v>
+        <v>2.566249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.055</v>
+        <v>-0.015</v>
       </c>
       <c r="N8" t="n">
-        <v>1.83625</v>
+        <v>2.605</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.12</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.05624999999999999</v>
+        <v>-0.05625000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>1.7</v>
@@ -1772,7 +1772,7 @@
         <v>0.27</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02375000000000001</v>
+        <v>0.02375</v>
       </c>
       <c r="N11" t="n">
         <v>2.538749999999999</v>
@@ -1899,7 +1899,7 @@
         <v>0.06</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02875000000000001</v>
+        <v>0.02875</v>
       </c>
       <c r="N12" t="n">
         <v>3.67875</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5521</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2808</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2487</v>
+      </c>
+      <c r="E75" t="n">
+        <v>321</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="G75" t="n">
+        <v>216</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.69%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>226</v>
+      </c>
+      <c r="K75" t="n">
+        <v>220</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.58625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.461538461538462</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.149999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.164772727272727</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.9081803005008346</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
